--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.84761165865756</v>
+        <v>7.450236894531853</v>
       </c>
       <c r="D2" t="n">
-        <v>35.84782102570265</v>
+        <v>5.825270916676681</v>
       </c>
       <c r="E2" t="n">
-        <v>12.38665913855498</v>
+        <v>2.012832110015184</v>
       </c>
       <c r="F2" t="n">
-        <v>8.201827101698427</v>
+        <v>1.332796904025994</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89559114378261</v>
+        <v>7.458033560864674</v>
       </c>
       <c r="D3" t="n">
-        <v>36.54048639695954</v>
+        <v>5.937829039505925</v>
       </c>
       <c r="E3" t="n">
-        <v>12.38665913855498</v>
+        <v>2.012832110015184</v>
       </c>
       <c r="F3" t="n">
-        <v>8.201827101698427</v>
+        <v>1.332796904025994</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.23522118150744</v>
+        <v>4.425723441994959</v>
       </c>
       <c r="D4" t="n">
-        <v>27.19592841447312</v>
+        <v>4.419338367351883</v>
       </c>
       <c r="E4" t="n">
-        <v>12.38665913855498</v>
+        <v>2.012832110015184</v>
       </c>
       <c r="F4" t="n">
-        <v>8.201827101698427</v>
+        <v>1.332796904025994</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.63099399037239</v>
+        <v>4.002536523435514</v>
       </c>
       <c r="D5" t="n">
-        <v>24.71645691840926</v>
+        <v>4.016424249241505</v>
       </c>
       <c r="E5" t="n">
-        <v>12.38665913855498</v>
+        <v>2.012832110015184</v>
       </c>
       <c r="F5" t="n">
-        <v>8.201827101698427</v>
+        <v>1.332796904025994</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.070400837473992</v>
+        <v>1.311440136089524</v>
       </c>
       <c r="D6" t="n">
-        <v>15.34278440114212</v>
+        <v>2.493202465185594</v>
       </c>
       <c r="E6" t="n">
-        <v>12.38665913855498</v>
+        <v>2.012832110015184</v>
       </c>
       <c r="F6" t="n">
-        <v>8.201827101698427</v>
+        <v>1.332796904025994</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>7.334372564307621</v>
+        <v>1.191835541699988</v>
       </c>
       <c r="D7" t="n">
-        <v>21.71359365220711</v>
+        <v>3.528458968483656</v>
       </c>
       <c r="E7" t="n">
-        <v>12.38665913855498</v>
+        <v>2.012832110015184</v>
       </c>
       <c r="F7" t="n">
-        <v>8.201827101698427</v>
+        <v>1.332796904025994</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.57791177676148</v>
+        <v>6.431410663723741</v>
       </c>
       <c r="D8" t="n">
-        <v>39.64109190072312</v>
+        <v>6.441677433867507</v>
       </c>
       <c r="E8" t="n">
-        <v>12.38665913855498</v>
+        <v>2.012832110015184</v>
       </c>
       <c r="F8" t="n">
-        <v>8.201827101698427</v>
+        <v>1.332796904025994</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.86758590194036</v>
+        <v>2.090982709065309</v>
       </c>
       <c r="D9" t="n">
-        <v>32.07418179469145</v>
+        <v>5.212054541637361</v>
       </c>
       <c r="E9" t="n">
-        <v>12.38665913855498</v>
+        <v>2.012832110015184</v>
       </c>
       <c r="F9" t="n">
-        <v>8.201827101698427</v>
+        <v>1.332796904025994</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.41122897924534</v>
+        <v>3.966824709127367</v>
       </c>
       <c r="D10" t="n">
-        <v>31.90025025395112</v>
+        <v>5.183790666267057</v>
       </c>
       <c r="E10" t="n">
-        <v>12.38665913855498</v>
+        <v>2.012832110015184</v>
       </c>
       <c r="F10" t="n">
-        <v>8.201827101698427</v>
+        <v>1.332796904025994</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>14.22073872824697</v>
+        <v>2.310870043340132</v>
       </c>
       <c r="D11" t="n">
-        <v>33.37097364992038</v>
+        <v>5.422783218112062</v>
       </c>
       <c r="E11" t="n">
-        <v>12.38665913855498</v>
+        <v>2.012832110015184</v>
       </c>
       <c r="F11" t="n">
-        <v>8.201827101698427</v>
+        <v>1.332796904025994</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.51175085443979</v>
+        <v>4.958159513846466</v>
       </c>
       <c r="D12" t="n">
-        <v>32.18200236990943</v>
+        <v>5.229575385110283</v>
       </c>
       <c r="E12" t="n">
-        <v>12.38665913855498</v>
+        <v>2.012832110015184</v>
       </c>
       <c r="F12" t="n">
-        <v>8.201827101698427</v>
+        <v>1.332796904025994</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.34978316462701</v>
+        <v>4.606839764251889</v>
       </c>
       <c r="D13" t="n">
-        <v>39.43486645079089</v>
+        <v>6.408165798253521</v>
       </c>
       <c r="E13" t="n">
-        <v>12.38665913855498</v>
+        <v>2.012832110015184</v>
       </c>
       <c r="F13" t="n">
-        <v>8.201827101698427</v>
+        <v>1.332796904025994</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>28.75262867691757</v>
+        <v>4.672302159999106</v>
       </c>
       <c r="D14" t="n">
-        <v>48.26266410999623</v>
+        <v>7.842682917874388</v>
       </c>
       <c r="E14" t="n">
-        <v>12.38665913855498</v>
+        <v>2.012832110015184</v>
       </c>
       <c r="F14" t="n">
-        <v>8.201827101698427</v>
+        <v>1.332796904025994</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
